--- a/data/latest/Weekly_Oil_Bulletin_Weekly_prices_without_taxes.xlsx
+++ b/data/latest/Weekly_Oil_Bulletin_Weekly_prices_without_taxes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E66FB0-347C-470B-A0AF-B04EB9EF7EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89853EF5-71E5-4EFD-B77C-06F26CC261B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
@@ -670,7 +670,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -696,13 +696,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>983.56</v>
+        <v>1006.9</v>
       </c>
       <c r="C3" s="3">
-        <v>1305.81</v>
+        <v>1325.81</v>
       </c>
       <c r="D3" s="3">
-        <v>1244.29</v>
+        <v>1261.44</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -713,20 +713,20 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1018.4611347107439</v>
+        <v>1033.948738016529</v>
       </c>
       <c r="C4" s="3">
-        <v>1340.9818958677688</v>
+        <v>1329.6595818181818</v>
       </c>
       <c r="D4" s="3">
-        <v>1244.2727272727275</v>
+        <v>1296.8347107438017</v>
       </c>
       <c r="E4" s="3">
-        <v>562.14</v>
+        <v>582.49</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>811.57024793388427</v>
+        <v>891.7355371900826</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -734,10 +734,10 @@
         <v>13</v>
       </c>
       <c r="B5" s="3">
-        <v>1022.6494310173515</v>
+        <v>1011.2327643506848</v>
       </c>
       <c r="C5" s="3">
-        <v>1247.1221114139096</v>
+        <v>1231.2054447472428</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -751,20 +751,20 @@
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1063.8899999999999</v>
+        <v>1045.3539999999998</v>
       </c>
       <c r="C6" s="3">
-        <v>1337.104</v>
+        <v>1313</v>
       </c>
       <c r="D6" s="3">
-        <v>1279.8600000000001</v>
+        <v>1239.8600000000001</v>
       </c>
       <c r="E6" s="3">
         <v>919.56</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>706.25</v>
+        <v>718.25</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -772,13 +772,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1095.6193277310924</v>
+        <v>1108.9638655462184</v>
       </c>
       <c r="C7" s="3">
-        <v>1365.1067226890757</v>
+        <v>1357.409243697479</v>
       </c>
       <c r="D7" s="3">
-        <v>1318.8557142857142</v>
+        <v>1324.9733613445378</v>
       </c>
       <c r="E7" s="3">
         <v>1041.81</v>
@@ -791,18 +791,18 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1001.1773547771406</v>
+        <v>1010.0121606973986</v>
       </c>
       <c r="C8" s="3">
-        <v>1285.7528582281013</v>
+        <v>1259.32814264576</v>
       </c>
       <c r="D8" s="3">
-        <v>1142.7000252773068</v>
+        <v>1175.2914179495147</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>646.81519450009057</v>
+        <v>677.88179558169247</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -810,13 +810,13 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>1366.3790220081612</v>
+        <v>1409.1346925670252</v>
       </c>
       <c r="C9" s="3">
-        <v>1420.6970365910765</v>
+        <v>1431.3426446192541</v>
       </c>
       <c r="D9" s="3">
-        <v>1484.8083483845076</v>
+        <v>1495.4513833146038</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -827,18 +827,18 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>977.54838709677415</v>
+        <v>957.38709677419354</v>
       </c>
       <c r="C10" s="3">
-        <v>1262.3225806451615</v>
+        <v>1195.3870967741937</v>
       </c>
       <c r="D10" s="3">
-        <v>1325.0645161290322</v>
+        <v>1317.8064516129032</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3">
-        <v>602.16129032258073</v>
+        <v>604.58064516129036</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -846,13 +846,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>1166.1082120679187</v>
+        <v>1125.256298809978</v>
       </c>
       <c r="C11" s="3">
-        <v>1523.6761001420402</v>
+        <v>1510.235790235422</v>
       </c>
       <c r="D11" s="3">
-        <v>1356.2589862771135</v>
+        <v>1375.5855688357681</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -863,18 +863,18 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>1152.8916666666667</v>
+        <v>1153.3166666666666</v>
       </c>
       <c r="C12" s="3">
-        <v>1355.4</v>
+        <v>1332.7083333333333</v>
       </c>
       <c r="D12" s="3">
-        <v>1422.6333333333332</v>
+        <v>1410.5416666666665</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>729.55000000000007</v>
+        <v>741.98333333333323</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -882,18 +882,18 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>1042.6781512605041</v>
+        <v>1198.2042016806722</v>
       </c>
       <c r="C13" s="3">
-        <v>1261.9176470588236</v>
+        <v>1415.7630252100839</v>
       </c>
       <c r="D13" s="3">
-        <v>1215.4563025210086</v>
+        <v>1191.6747899159664</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>560.51260504201673</v>
+        <v>631.10084033613452</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -901,10 +901,10 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>1061.2729032258062</v>
+        <v>1058.0470967741935</v>
       </c>
       <c r="C14" s="3">
-        <v>1322.4441935483871</v>
+        <v>1283.7345161290323</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3">
@@ -918,20 +918,20 @@
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>971.14027318871513</v>
+        <v>990.76108597054667</v>
       </c>
       <c r="C15" s="3">
-        <v>1161.231975542717</v>
+        <v>1169.4953616896994</v>
       </c>
       <c r="D15" s="3">
-        <v>1161.231975542717</v>
+        <v>1169.4953616896994</v>
       </c>
       <c r="E15" s="3">
-        <v>1272.2811310494833</v>
+        <v>1281.5846410867362</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>672.92630647619865</v>
+        <v>696.53373766411164</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -956,20 +956,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>1026.034426229508</v>
+        <v>983.67377049180323</v>
       </c>
       <c r="C17" s="3">
-        <v>1240.5918032786885</v>
+        <v>1163.7639344262295</v>
       </c>
       <c r="D17" s="3">
-        <v>1287.8555737704917</v>
+        <v>1279.5768852459016</v>
       </c>
       <c r="E17" s="3">
-        <v>682.34</v>
+        <v>715.7</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>484.36114754098361</v>
+        <v>492.96770491803284</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -977,18 +977,18 @@
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1069.6581818181819</v>
+        <v>1053.459834710744</v>
       </c>
       <c r="C18" s="3">
-        <v>1354.4888429752066</v>
+        <v>1314.6871900826445</v>
       </c>
       <c r="D18" s="3">
-        <v>1354.4888429752068</v>
+        <v>1314.6789256198349</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>550.33768595041329</v>
+        <v>581.20545454545459</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -996,18 +996,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1039.6363636363637</v>
+        <v>1028.8595041322315</v>
       </c>
       <c r="C19" s="3">
-        <v>1298.2512396694212</v>
+        <v>1268.7884297520663</v>
       </c>
       <c r="D19" s="3">
-        <v>1172.9702479338844</v>
+        <v>1174.9123966942147</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>478.59438016528918</v>
+        <v>507.10677685950407</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1015,18 +1015,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="3">
-        <v>1043.70587008547</v>
+        <v>1077.0392034188035</v>
       </c>
       <c r="C20" s="3">
-        <v>1336.254658119658</v>
+        <v>1325.9982478632478</v>
       </c>
       <c r="D20" s="3">
-        <v>1219.83</v>
+        <v>1217.1984210526316</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>642.87075851851853</v>
+        <v>725.27816592592592</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1051,16 +1051,16 @@
         <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>1161.7768595041321</v>
+        <v>1186.6776859504132</v>
       </c>
       <c r="C22" s="3">
-        <v>1513.1239669421486</v>
+        <v>1493.1239669421489</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>584.74132231404951</v>
+        <v>589.84876033057844</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1068,22 +1068,22 @@
         <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1057.8380010342964</v>
+        <v>1105.1608796206601</v>
       </c>
       <c r="C23" s="3">
-        <v>1310.9965774571856</v>
+        <v>1339.3938558894695</v>
       </c>
       <c r="D23" s="3">
-        <v>1298.8733715674773</v>
+        <v>1322.2708119118909</v>
       </c>
       <c r="E23" s="3">
-        <v>840.22129565583657</v>
+        <v>737.69426082191342</v>
       </c>
       <c r="F23" s="3">
-        <v>614.676472144331</v>
+        <v>639.67702162768489</v>
       </c>
       <c r="G23" s="3">
-        <v>488.61868657536496</v>
+        <v>515.84817030731051</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1091,20 +1091,20 @@
         <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>1104.6121367121871</v>
+        <v>1136.8593724845446</v>
       </c>
       <c r="C24" s="3">
-        <v>1314.2919484142033</v>
+        <v>1307.8708915036341</v>
       </c>
       <c r="D24" s="3">
-        <v>1288.529346788187</v>
+        <v>1271.4561760564798</v>
       </c>
       <c r="E24" s="3">
-        <v>874.18461200000002</v>
+        <v>868.63461200000006</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>577.79072273195936</v>
+        <v>587.54682029293497</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1112,20 +1112,20 @@
         <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>985.57427430991515</v>
+        <v>994.96158890762604</v>
       </c>
       <c r="C25" s="3">
-        <v>1299.7395198920601</v>
+        <v>1292.9436012741241</v>
       </c>
       <c r="D25" s="3">
-        <v>1291.8126791971965</v>
+        <v>1284.5980888139404</v>
       </c>
       <c r="E25" s="3">
-        <v>1022.8116859996627</v>
+        <v>994.19711448379246</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>798.31531210764024</v>
+        <v>628.80269814502537</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1133,16 +1133,16 @@
         <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>946.35</v>
+        <v>947.16300813008138</v>
       </c>
       <c r="C26" s="3">
-        <v>1195.6020325203253</v>
+        <v>1152.5126016260162</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
-        <v>566.76065040650406</v>
+        <v>605.78504065040647</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1150,18 +1150,18 @@
         <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>1005.4857377049179</v>
+        <v>1004.1660655737705</v>
       </c>
       <c r="C27" s="3">
-        <v>1270.8521311475411</v>
+        <v>1219.0324590163934</v>
       </c>
       <c r="D27" s="3">
-        <v>1292.5793442622951</v>
+        <v>1244.1613114754098</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>670.01786885245906</v>
+        <v>668.37852459016392</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1169,20 +1169,20 @@
         <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1212.6333514958678</v>
+        <v>1206.2725664958677</v>
       </c>
       <c r="C28" s="3">
-        <v>1405.8252474958679</v>
+        <v>1382.4643114958678</v>
       </c>
       <c r="D28" s="3">
-        <v>1214.8173553719007</v>
+        <v>1173.4611570247935</v>
       </c>
       <c r="E28" s="3">
-        <v>669.78</v>
+        <v>636.06899999999996</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>874.61215454545459</v>
+        <v>875.79894049586778</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1190,16 +1190,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1059.0713174850034</v>
+        <v>1140.5349886125127</v>
       </c>
       <c r="C29" s="3">
-        <v>1555.6187513885804</v>
+        <v>1500.3081320055373</v>
       </c>
       <c r="D29" s="3">
-        <v>1182.4501221950679</v>
+        <v>1113.276470325548</v>
       </c>
       <c r="E29" s="3">
-        <v>713.06376360808713</v>
+        <v>656.99102398070818</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1209,22 +1209,22 @@
         <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>1075.6152815704174</v>
+        <v>1112.6427395865062</v>
       </c>
       <c r="C30" s="5">
-        <v>1324.1080528133259</v>
+        <v>1331.8558137396981</v>
       </c>
       <c r="D30" s="5">
-        <v>1259.7129725913101</v>
+        <v>1251.6023539564812</v>
       </c>
       <c r="E30" s="5">
-        <v>667.06435813066525</v>
+        <v>639.52560270855781</v>
       </c>
       <c r="F30" s="5">
-        <v>614.676472144331</v>
+        <v>639.67702162768489</v>
       </c>
       <c r="G30" s="5">
-        <v>550.71855180095986</v>
+        <v>571.18839318974278</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
@@ -1232,20 +1232,20 @@
         <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>1078.7971794792707</v>
+        <v>1114.6595657937769</v>
       </c>
       <c r="C31" s="5">
-        <v>1322.9637481682562</v>
+        <v>1331.5370991092184</v>
       </c>
       <c r="D31" s="5">
-        <v>1252.7879043946693</v>
+        <v>1244.0569938220312</v>
       </c>
       <c r="E31" s="5">
-        <v>700.5667543000435</v>
+        <v>677.34021826223773</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>559.85165673929555</v>
+        <v>582.19646468694634</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest/Weekly_Oil_Bulletin_Weekly_prices_without_taxes.xlsx
+++ b/data/latest/Weekly_Oil_Bulletin_Weekly_prices_without_taxes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89853EF5-71E5-4EFD-B77C-06F26CC261B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE35B6AC-4D5F-4A80-8B3C-E5709D20552C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
@@ -670,7 +670,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -696,13 +696,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>1006.9</v>
+        <v>966.9</v>
       </c>
       <c r="C3" s="3">
-        <v>1325.81</v>
+        <v>1300.81</v>
       </c>
       <c r="D3" s="3">
-        <v>1261.44</v>
+        <v>1251.28</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -713,16 +713,16 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1033.948738016529</v>
+        <v>1043.3784900826447</v>
       </c>
       <c r="C4" s="3">
-        <v>1329.6595818181818</v>
+        <v>1342.4364413223141</v>
       </c>
       <c r="D4" s="3">
-        <v>1296.8347107438017</v>
+        <v>1253.8595041322315</v>
       </c>
       <c r="E4" s="3">
-        <v>582.49</v>
+        <v>589.69999999999993</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
@@ -734,10 +734,10 @@
         <v>13</v>
       </c>
       <c r="B5" s="3">
-        <v>1011.2327643506848</v>
+        <v>1008.8994310173515</v>
       </c>
       <c r="C5" s="3">
-        <v>1231.2054447472428</v>
+        <v>1239.4554447472428</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -751,20 +751,20 @@
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1045.3539999999998</v>
+        <v>1047.8899999999999</v>
       </c>
       <c r="C6" s="3">
-        <v>1313</v>
+        <v>1303.3040000000001</v>
       </c>
       <c r="D6" s="3">
         <v>1239.8600000000001</v>
       </c>
       <c r="E6" s="3">
-        <v>919.56</v>
+        <v>954.56</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>718.25</v>
+        <v>774.25</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -772,13 +772,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1108.9638655462184</v>
+        <v>1108.9470588235295</v>
       </c>
       <c r="C7" s="3">
-        <v>1357.409243697479</v>
+        <v>1355.0142857142857</v>
       </c>
       <c r="D7" s="3">
-        <v>1324.9733613445378</v>
+        <v>1328.2170588235294</v>
       </c>
       <c r="E7" s="3">
         <v>1041.81</v>
@@ -791,18 +791,18 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1010.0121606973986</v>
+        <v>1011.5284214614618</v>
       </c>
       <c r="C8" s="3">
-        <v>1259.32814264576</v>
+        <v>1285.2708009463918</v>
       </c>
       <c r="D8" s="3">
-        <v>1175.2914179495147</v>
+        <v>1171.5997199799151</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>677.88179558169247</v>
+        <v>701.15019404156089</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -810,13 +810,13 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>1409.1346925670252</v>
+        <v>1366.3424619048258</v>
       </c>
       <c r="C9" s="3">
-        <v>1431.3426446192541</v>
+        <v>1431.361793784366</v>
       </c>
       <c r="D9" s="3">
-        <v>1495.4513833146038</v>
+        <v>1495.4713901561267</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -827,13 +827,13 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>957.38709677419354</v>
+        <v>984.80645161290317</v>
       </c>
       <c r="C10" s="3">
-        <v>1195.3870967741937</v>
+        <v>1234.9032258064517</v>
       </c>
       <c r="D10" s="3">
-        <v>1317.8064516129032</v>
+        <v>1342</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -846,13 +846,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>1125.256298809978</v>
+        <v>1132.0591270228178</v>
       </c>
       <c r="C11" s="3">
-        <v>1510.235790235422</v>
+        <v>1506.8529579282874</v>
       </c>
       <c r="D11" s="3">
-        <v>1375.5855688357681</v>
+        <v>1385.1920318725101</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -863,18 +863,18 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>1153.3166666666666</v>
+        <v>1167.2</v>
       </c>
       <c r="C12" s="3">
-        <v>1332.7083333333333</v>
+        <v>1347.3666666666668</v>
       </c>
       <c r="D12" s="3">
-        <v>1410.5416666666665</v>
+        <v>1442.3833333333332</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>741.98333333333323</v>
+        <v>747.00000000000011</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -882,18 +882,18 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>1198.2042016806722</v>
+        <v>1168.79243697479</v>
       </c>
       <c r="C13" s="3">
-        <v>1415.7630252100839</v>
+        <v>1412.4016806722689</v>
       </c>
       <c r="D13" s="3">
-        <v>1191.6747899159664</v>
+        <v>1204.0277310924371</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>631.10084033613452</v>
+        <v>599.37815126050418</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -901,12 +901,14 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>1058.0470967741935</v>
+        <v>1051.5954838709677</v>
       </c>
       <c r="C14" s="3">
-        <v>1283.7345161290323</v>
-      </c>
-      <c r="D14" s="3"/>
+        <v>1290.1861290322581</v>
+      </c>
+      <c r="D14" s="3">
+        <v>968.11387096774195</v>
+      </c>
       <c r="E14" s="3">
         <v>619.89</v>
       </c>
@@ -918,20 +920,20 @@
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>990.76108597054667</v>
+        <v>1002.051500729686</v>
       </c>
       <c r="C15" s="3">
-        <v>1169.4953616896994</v>
+        <v>1175.1106788129641</v>
       </c>
       <c r="D15" s="3">
-        <v>1169.4953616896994</v>
+        <v>1175.1106788129641</v>
       </c>
       <c r="E15" s="3">
-        <v>1281.5846410867362</v>
+        <v>1421.5602641717117</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>696.53373766411164</v>
+        <v>701.42190217257621</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -939,13 +941,13 @@
         <v>24</v>
       </c>
       <c r="B16" s="3">
-        <v>1108.0712195121951</v>
+        <v>1098.3964227642275</v>
       </c>
       <c r="C16" s="3">
-        <v>1386.2556910569103</v>
+        <v>1364.3044715447152</v>
       </c>
       <c r="D16" s="3">
-        <v>1116.292422907489</v>
+        <v>1194.4422026431719</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -956,20 +958,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>983.67377049180323</v>
+        <v>979.34590163934422</v>
       </c>
       <c r="C17" s="3">
-        <v>1163.7639344262295</v>
+        <v>1166.8049180327871</v>
       </c>
       <c r="D17" s="3">
-        <v>1279.5768852459016</v>
+        <v>1294.3309836065573</v>
       </c>
       <c r="E17" s="3">
-        <v>715.7</v>
+        <v>732.25</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>492.96770491803284</v>
+        <v>497.05786885245902</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -977,18 +979,18 @@
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1053.459834710744</v>
+        <v>1058.2532231404957</v>
       </c>
       <c r="C18" s="3">
-        <v>1314.6871900826445</v>
+        <v>1306.8359504132231</v>
       </c>
       <c r="D18" s="3">
-        <v>1314.6789256198349</v>
+        <v>1306.8276859504133</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>581.20545454545459</v>
+        <v>620.37900826446275</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -996,18 +998,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1028.8595041322315</v>
+        <v>1050.4214876033056</v>
       </c>
       <c r="C19" s="3">
-        <v>1268.7884297520663</v>
+        <v>1280.3752066115703</v>
       </c>
       <c r="D19" s="3">
-        <v>1174.9123966942147</v>
+        <v>1169.2264462809917</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>507.10677685950407</v>
+        <v>542.20595041322315</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1015,18 +1017,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="3">
-        <v>1077.0392034188035</v>
+        <v>1001.8255282051282</v>
       </c>
       <c r="C20" s="3">
-        <v>1325.9982478632478</v>
+        <v>1356.7674786324787</v>
       </c>
       <c r="D20" s="3">
-        <v>1217.1984210526316</v>
+        <v>1251.4089473684212</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>725.27816592592592</v>
+        <v>756.75964740740733</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1051,16 +1053,16 @@
         <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>1186.6776859504132</v>
+        <v>1127.8181818181815</v>
       </c>
       <c r="C22" s="3">
-        <v>1493.1239669421489</v>
+        <v>1471.9669421487606</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>589.84876033057844</v>
+        <v>608.90661157024795</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1068,22 +1070,22 @@
         <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1105.1608796206601</v>
+        <v>1094.6447089459189</v>
       </c>
       <c r="C23" s="3">
-        <v>1339.3938558894695</v>
+        <v>1334.4661322905097</v>
       </c>
       <c r="D23" s="3">
-        <v>1322.2708119118909</v>
+        <v>1334.0478463024263</v>
       </c>
       <c r="E23" s="3">
-        <v>737.69426082191342</v>
+        <v>824.97058607932775</v>
       </c>
       <c r="F23" s="3">
-        <v>639.67702162768489</v>
+        <v>668.65003973627688</v>
       </c>
       <c r="G23" s="3">
-        <v>515.84817030731051</v>
+        <v>542.14060598416847</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1091,20 +1093,20 @@
         <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>1136.8593724845446</v>
+        <v>1121.7762830536503</v>
       </c>
       <c r="C24" s="3">
-        <v>1307.8708915036341</v>
+        <v>1335.4621110158291</v>
       </c>
       <c r="D24" s="3">
-        <v>1271.4561760564798</v>
+        <v>1303.1634931296503</v>
       </c>
       <c r="E24" s="3">
-        <v>868.63461200000006</v>
+        <v>891.18461200000002</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>587.54682029293497</v>
+        <v>602.18096663439837</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1112,20 +1114,20 @@
         <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>994.96158890762604</v>
+        <v>991.94014719134884</v>
       </c>
       <c r="C25" s="3">
-        <v>1292.9436012741241</v>
+        <v>1294.679333133073</v>
       </c>
       <c r="D25" s="3">
-        <v>1284.5980888139404</v>
+        <v>1232.7331781315711</v>
       </c>
       <c r="E25" s="3">
-        <v>994.19711448379246</v>
+        <v>954.55279363172133</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>628.80269814502537</v>
+        <v>630.16859417242426</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1133,16 +1135,16 @@
         <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>947.16300813008138</v>
+        <v>978.87032520325204</v>
       </c>
       <c r="C26" s="3">
-        <v>1152.5126016260162</v>
+        <v>1179.3418699186991</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
-        <v>605.78504065040647</v>
+        <v>608.22406504065043</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1150,18 +1152,18 @@
         <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>1004.1660655737705</v>
+        <v>995.27262295081982</v>
       </c>
       <c r="C27" s="3">
-        <v>1219.0324590163934</v>
+        <v>1198.6062295081965</v>
       </c>
       <c r="D27" s="3">
-        <v>1244.1613114754098</v>
+        <v>1232.7432786885245</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>668.37852459016392</v>
+        <v>678.55065573770491</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1169,20 +1171,20 @@
         <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1206.2725664958677</v>
+        <v>1198.7763774958676</v>
       </c>
       <c r="C28" s="3">
-        <v>1382.4643114958678</v>
+        <v>1382.3398754958678</v>
       </c>
       <c r="D28" s="3">
-        <v>1173.4611570247935</v>
+        <v>1236.2991735537189</v>
       </c>
       <c r="E28" s="3">
-        <v>636.06899999999996</v>
+        <v>646.21</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>875.79894049586778</v>
+        <v>877.70914297520676</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1190,16 +1192,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1140.5349886125127</v>
+        <v>1096.7219020172913</v>
       </c>
       <c r="C29" s="3">
-        <v>1500.3081320055373</v>
+        <v>1491.6966858789626</v>
       </c>
       <c r="D29" s="3">
-        <v>1113.276470325548</v>
+        <v>1142.0028818443805</v>
       </c>
       <c r="E29" s="3">
-        <v>656.99102398070818</v>
+        <v>687.95028818443814</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1209,22 +1211,22 @@
         <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>1112.6427395865062</v>
+        <v>1096.8691243628789</v>
       </c>
       <c r="C30" s="5">
-        <v>1331.8558137396981</v>
+        <v>1333.9618446006982</v>
       </c>
       <c r="D30" s="5">
-        <v>1251.6023539564812</v>
+        <v>1254.5940739215507</v>
       </c>
       <c r="E30" s="5">
-        <v>639.52560270855781</v>
+        <v>650.85157980614304</v>
       </c>
       <c r="F30" s="5">
-        <v>639.67702162768489</v>
+        <v>668.65003973627688</v>
       </c>
       <c r="G30" s="5">
-        <v>571.18839318974278</v>
+        <v>575.56150015170238</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
@@ -1232,20 +1234,20 @@
         <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>1114.6595657937769</v>
+        <v>1098.3785742966982</v>
       </c>
       <c r="C31" s="5">
-        <v>1331.5370991092184</v>
+        <v>1333.9721704507849</v>
       </c>
       <c r="D31" s="5">
-        <v>1244.0569938220312</v>
+        <v>1246.873782598014</v>
       </c>
       <c r="E31" s="5">
-        <v>677.34021826223773</v>
+        <v>688.19767184609452</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>582.19646468694634</v>
+        <v>581.03740080752027</v>
       </c>
     </row>
   </sheetData>

--- a/data/latest/Weekly_Oil_Bulletin_Weekly_prices_without_taxes.xlsx
+++ b/data/latest/Weekly_Oil_Bulletin_Weekly_prices_without_taxes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\A\4\MAT-Market Analysis Team\WOB - Weekly Oil Bulletin\WOB proces new 2024-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE35B6AC-4D5F-4A80-8B3C-E5709D20552C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F14B4348-0AEF-4D74-AAB3-B7CC9FD28FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{220E869B-DB88-4652-934E-25EDB3CABDE3}"/>
   </bookViews>
@@ -670,7 +670,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -696,13 +696,13 @@
         <v>11</v>
       </c>
       <c r="B3" s="3">
-        <v>966.9</v>
+        <v>929.4</v>
       </c>
       <c r="C3" s="3">
         <v>1300.81</v>
       </c>
       <c r="D3" s="3">
-        <v>1251.28</v>
+        <v>1269.3599999999999</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -713,20 +713,20 @@
         <v>12</v>
       </c>
       <c r="B4" s="3">
-        <v>1043.3784900826447</v>
+        <v>1013.85782892562</v>
       </c>
       <c r="C4" s="3">
-        <v>1342.4364413223141</v>
+        <v>1362.6926396694216</v>
       </c>
       <c r="D4" s="3">
-        <v>1253.8595041322315</v>
+        <v>1250.7190082644629</v>
       </c>
       <c r="E4" s="3">
-        <v>589.69999999999993</v>
+        <v>609.72</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3">
-        <v>891.7355371900826</v>
+        <v>885.12396694214874</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -734,10 +734,10 @@
         <v>13</v>
       </c>
       <c r="B5" s="3">
-        <v>1008.8994310173515</v>
+        <v>991.14943101735162</v>
       </c>
       <c r="C5" s="3">
-        <v>1239.4554447472428</v>
+        <v>1244.8721114139096</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -751,20 +751,20 @@
         <v>14</v>
       </c>
       <c r="B6" s="3">
-        <v>1047.8899999999999</v>
+        <v>1025.3539999999998</v>
       </c>
       <c r="C6" s="3">
-        <v>1303.3040000000001</v>
+        <v>1353.7040000000002</v>
       </c>
       <c r="D6" s="3">
-        <v>1239.8600000000001</v>
+        <v>1271.8600000000001</v>
       </c>
       <c r="E6" s="3">
         <v>954.56</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3">
-        <v>774.25</v>
+        <v>814.25</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -772,13 +772,13 @@
         <v>15</v>
       </c>
       <c r="B7" s="3">
-        <v>1108.9470588235295</v>
+        <v>1083.6697478991596</v>
       </c>
       <c r="C7" s="3">
-        <v>1355.0142857142857</v>
+        <v>1344.1319327731094</v>
       </c>
       <c r="D7" s="3">
-        <v>1328.2170588235294</v>
+        <v>1301.3672268907562</v>
       </c>
       <c r="E7" s="3">
         <v>1041.81</v>
@@ -791,18 +791,18 @@
         <v>16</v>
       </c>
       <c r="B8" s="3">
-        <v>1011.5284214614618</v>
+        <v>959.27321291886574</v>
       </c>
       <c r="C8" s="3">
-        <v>1285.2708009463918</v>
+        <v>1282.4412129080131</v>
       </c>
       <c r="D8" s="3">
-        <v>1171.5997199799151</v>
+        <v>1196.005523207408</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3">
-        <v>701.15019404156089</v>
+        <v>700.87691006966247</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -810,7 +810,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="3">
-        <v>1366.3424619048258</v>
+        <v>1302.1258378262673</v>
       </c>
       <c r="C9" s="3">
         <v>1431.361793784366</v>
@@ -827,13 +827,13 @@
         <v>18</v>
       </c>
       <c r="B10" s="3">
-        <v>984.80645161290317</v>
+        <v>930.77419354838707</v>
       </c>
       <c r="C10" s="3">
-        <v>1234.9032258064517</v>
+        <v>1266.3548387096773</v>
       </c>
       <c r="D10" s="3">
-        <v>1342</v>
+        <v>1342.8064516129032</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -846,13 +846,13 @@
         <v>19</v>
       </c>
       <c r="B11" s="3">
-        <v>1132.0591270228178</v>
+        <v>1146.8363816407104</v>
       </c>
       <c r="C11" s="3">
-        <v>1506.8529579282874</v>
+        <v>1519.3455960713666</v>
       </c>
       <c r="D11" s="3">
-        <v>1385.1920318725101</v>
+        <v>1391.3777335104025</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -863,18 +863,18 @@
         <v>20</v>
       </c>
       <c r="B12" s="3">
-        <v>1167.2</v>
+        <v>1127.0333333333333</v>
       </c>
       <c r="C12" s="3">
-        <v>1347.3666666666668</v>
+        <v>1352.1083333333336</v>
       </c>
       <c r="D12" s="3">
-        <v>1442.3833333333332</v>
+        <v>1459.8583333333333</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3">
-        <v>747.00000000000011</v>
+        <v>751.96666666666658</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -882,18 +882,18 @@
         <v>21</v>
       </c>
       <c r="B13" s="3">
-        <v>1168.79243697479</v>
+        <v>1158.7084033613446</v>
       </c>
       <c r="C13" s="3">
-        <v>1412.4016806722689</v>
+        <v>1439.29243697479</v>
       </c>
       <c r="D13" s="3">
-        <v>1204.0277310924371</v>
+        <v>1235.372268907563</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3">
-        <v>599.37815126050418</v>
+        <v>628.78991596638662</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -901,13 +901,13 @@
         <v>22</v>
       </c>
       <c r="B14" s="3">
-        <v>1051.5954838709677</v>
+        <v>1012.8858064516129</v>
       </c>
       <c r="C14" s="3">
-        <v>1290.1861290322581</v>
+        <v>1290.9925806451613</v>
       </c>
       <c r="D14" s="3">
-        <v>968.11387096774195</v>
+        <v>965.69451612903219</v>
       </c>
       <c r="E14" s="3">
         <v>619.89</v>
@@ -920,20 +920,20 @@
         <v>23</v>
       </c>
       <c r="B15" s="3">
-        <v>1002.051500729686</v>
+        <v>993.17488636324219</v>
       </c>
       <c r="C15" s="3">
-        <v>1175.1106788129641</v>
+        <v>1162.0716347614493</v>
       </c>
       <c r="D15" s="3">
-        <v>1175.1106788129641</v>
+        <v>1162.0716347614493</v>
       </c>
       <c r="E15" s="3">
-        <v>1421.5602641717117</v>
+        <v>1463.0425908286841</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3">
-        <v>701.42190217257621</v>
+        <v>703.11833091938286</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -958,20 +958,20 @@
         <v>25</v>
       </c>
       <c r="B17" s="3">
-        <v>979.34590163934422</v>
+        <v>971.22295081967218</v>
       </c>
       <c r="C17" s="3">
-        <v>1166.8049180327871</v>
+        <v>1268.6655737704918</v>
       </c>
       <c r="D17" s="3">
-        <v>1294.3309836065573</v>
+        <v>1297.3719672131149</v>
       </c>
       <c r="E17" s="3">
-        <v>732.25</v>
+        <v>745.88</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3">
-        <v>497.05786885245902</v>
+        <v>499.42672131147538</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -979,18 +979,18 @@
         <v>26</v>
       </c>
       <c r="B18" s="3">
-        <v>1058.2532231404957</v>
+        <v>1044.8647933884299</v>
       </c>
       <c r="C18" s="3">
-        <v>1306.8359504132231</v>
+        <v>1324.050826446281</v>
       </c>
       <c r="D18" s="3">
-        <v>1306.8276859504133</v>
+        <v>1324.050826446281</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3">
-        <v>620.37900826446275</v>
+        <v>636.49471074380165</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -998,18 +998,18 @@
         <v>27</v>
       </c>
       <c r="B19" s="3">
-        <v>1050.4214876033056</v>
+        <v>1030.4628099173556</v>
       </c>
       <c r="C19" s="3">
-        <v>1280.3752066115703</v>
+        <v>1283.1107438016529</v>
       </c>
       <c r="D19" s="3">
-        <v>1169.2264462809917</v>
+        <v>1196.3338842975209</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3">
-        <v>542.20595041322315</v>
+        <v>564.08198347107441</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1017,18 +1017,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="3">
-        <v>1001.8255282051282</v>
+        <v>965.92809230769228</v>
       </c>
       <c r="C20" s="3">
-        <v>1356.7674786324787</v>
+        <v>1333.6905555555554</v>
       </c>
       <c r="D20" s="3">
-        <v>1251.4089473684212</v>
+        <v>1224.2159649122807</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3">
-        <v>756.75964740740733</v>
+        <v>747.5003881481482</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1053,16 +1053,16 @@
         <v>30</v>
       </c>
       <c r="B22" s="3">
-        <v>1127.8181818181815</v>
+        <v>1063.1652892561985</v>
       </c>
       <c r="C22" s="3">
-        <v>1471.9669421487606</v>
+        <v>1482.520661157025</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3">
-        <v>608.90661157024795</v>
+        <v>619.77438016528924</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1070,22 +1070,22 @@
         <v>31</v>
       </c>
       <c r="B23" s="3">
-        <v>1094.6447089459189</v>
+        <v>1011.190419721688</v>
       </c>
       <c r="C23" s="3">
-        <v>1334.4661322905097</v>
+        <v>1328.2696089067856</v>
       </c>
       <c r="D23" s="3">
-        <v>1334.0478463024263</v>
+        <v>1357.1557010815122</v>
       </c>
       <c r="E23" s="3">
-        <v>824.97058607932775</v>
+        <v>851.76438530360133</v>
       </c>
       <c r="F23" s="3">
-        <v>668.65003973627688</v>
+        <v>670.36196012534617</v>
       </c>
       <c r="G23" s="3">
-        <v>542.14060598416847</v>
+        <v>548.51646998768126</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1093,20 +1093,20 @@
         <v>32</v>
       </c>
       <c r="B24" s="3">
-        <v>1121.7762830536503</v>
+        <v>1063.3888033788535</v>
       </c>
       <c r="C24" s="3">
-        <v>1335.4621110158291</v>
+        <v>1348.2042248369676</v>
       </c>
       <c r="D24" s="3">
-        <v>1303.1634931296503</v>
+        <v>1319.4236557312765</v>
       </c>
       <c r="E24" s="3">
-        <v>891.18461200000002</v>
+        <v>919.72461199999998</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3">
-        <v>602.18096663439837</v>
+        <v>607.87202354496753</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1114,20 +1114,20 @@
         <v>33</v>
       </c>
       <c r="B25" s="3">
-        <v>991.94014719134884</v>
+        <v>986.86065865015996</v>
       </c>
       <c r="C25" s="3">
-        <v>1294.679333133073</v>
+        <v>1289.7406167598601</v>
       </c>
       <c r="D25" s="3">
-        <v>1232.7331781315711</v>
+        <v>1294.6047538009839</v>
       </c>
       <c r="E25" s="3">
-        <v>954.55279363172133</v>
+        <v>933.0166626147776</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3">
-        <v>630.16859417242426</v>
+        <v>627.54100200100993</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1135,16 +1135,16 @@
         <v>34</v>
       </c>
       <c r="B26" s="3">
-        <v>978.87032520325204</v>
+        <v>926.02479674796746</v>
       </c>
       <c r="C26" s="3">
-        <v>1179.3418699186991</v>
+        <v>1193.9760162601626</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3">
-        <v>608.22406504065043</v>
+        <v>609.85008130081303</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1152,18 +1152,18 @@
         <v>35</v>
       </c>
       <c r="B27" s="3">
-        <v>995.27262295081982</v>
+        <v>979.96934426229518</v>
       </c>
       <c r="C27" s="3">
-        <v>1198.6062295081965</v>
+        <v>1211.5980327868851</v>
       </c>
       <c r="D27" s="3">
-        <v>1232.7432786885245</v>
+        <v>1247.505573770492</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3">
-        <v>678.55065573770491</v>
+        <v>693.5506557377048</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1171,20 +1171,20 @@
         <v>36</v>
       </c>
       <c r="B28" s="3">
-        <v>1198.7763774958676</v>
+        <v>1174.5064234958677</v>
       </c>
       <c r="C28" s="3">
-        <v>1382.3398754958678</v>
+        <v>1381.1643894958677</v>
       </c>
       <c r="D28" s="3">
-        <v>1236.2991735537189</v>
+        <v>1225.2421487603308</v>
       </c>
       <c r="E28" s="3">
-        <v>646.21</v>
+        <v>734.6</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3">
-        <v>877.70914297520676</v>
+        <v>879.03558016528928</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1192,16 +1192,16 @@
         <v>37</v>
       </c>
       <c r="B29" s="3">
-        <v>1096.7219020172913</v>
+        <v>1033.7119001660906</v>
       </c>
       <c r="C29" s="3">
-        <v>1491.6966858789626</v>
+        <v>1489.6619832113838</v>
       </c>
       <c r="D29" s="3">
-        <v>1142.0028818443805</v>
+        <v>1139.7584953090632</v>
       </c>
       <c r="E29" s="3">
-        <v>687.95028818443814</v>
+        <v>676.30291331866954</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1211,22 +1211,22 @@
         <v>9</v>
       </c>
       <c r="B30" s="5">
-        <v>1096.8691243628789</v>
+        <v>1065.3667692159358</v>
       </c>
       <c r="C30" s="5">
-        <v>1333.9618446006982</v>
+        <v>1353.1272538652133</v>
       </c>
       <c r="D30" s="5">
-        <v>1254.5940739215507</v>
+        <v>1271.8374019161199</v>
       </c>
       <c r="E30" s="5">
-        <v>650.85157980614304</v>
+        <v>714.47525534511033</v>
       </c>
       <c r="F30" s="5">
-        <v>668.65003973627688</v>
+        <v>670.36196012534617</v>
       </c>
       <c r="G30" s="5">
-        <v>575.56150015170238</v>
+        <v>584.03119691518157</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
@@ -1234,20 +1234,20 @@
         <v>10</v>
       </c>
       <c r="B31" s="5">
-        <v>1098.3785742966982</v>
+        <v>1075.4129322604331</v>
       </c>
       <c r="C31" s="5">
-        <v>1333.9721704507849</v>
+        <v>1359.0933398248055</v>
       </c>
       <c r="D31" s="5">
-        <v>1246.873782598014</v>
+        <v>1264.3786882607387</v>
       </c>
       <c r="E31" s="5">
-        <v>688.19767184609452</v>
+        <v>757.66047013889852</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5">
-        <v>581.03740080752027</v>
+        <v>590.34642438031165</v>
       </c>
     </row>
   </sheetData>
